--- a/artfynd/A 47667-2020 artfynd.xlsx
+++ b/artfynd/A 47667-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47667-2020 artfynd.xlsx
+++ b/artfynd/A 47667-2020 artfynd.xlsx
@@ -1191,7 +1191,7 @@
         <v>67841600</v>
       </c>
       <c r="B6" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438948.2731027678</v>
+        <v>438948</v>
       </c>
       <c r="R6" t="n">
-        <v>6673585.029387403</v>
+        <v>6673585</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,19 +1266,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5235,7 +5225,7 @@
         <v>67841558</v>
       </c>
       <c r="B40" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5277,10 +5267,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439090.3206403665</v>
+        <v>439090</v>
       </c>
       <c r="R40" t="n">
-        <v>6674067.575082696</v>
+        <v>6674068</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5310,19 +5300,9 @@
           <t>2017-10-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2017-10-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
